--- a/photography_forms/034_photography_studio_client_contact_form--photography_forms.xlsx
+++ b/photography_forms/034_photography_studio_client_contact_form--photography_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>time_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Time 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>text_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>integer_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>decimal_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1216,80 +1216,114 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>select_multiple_2_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>select_multiple_2_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
